--- a/files/港岛-山顶区-Twelve Peaks.xlsx
+++ b/files/港岛-山顶区-Twelve Peaks.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +42,76 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +122,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -98,6 +196,42 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -465,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -542,7 +676,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2号屋</t>
+          <t>1号屋</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -561,7 +695,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>4479</v>
+        <v>4858</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -574,10 +708,10 @@
         </is>
       </c>
       <c r="H3" s="5" t="n">
-        <v>495100000</v>
+        <v>666523000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>110538</v>
+        <v>137201</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -588,7 +722,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>3号屋</t>
+          <t>2号屋</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -607,11 +741,11 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4945</v>
+        <v>4479</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -619,26 +753,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H4" s="5" t="n">
+        <v>495100000</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>110538</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>5号屋</t>
+          <t>3号屋</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -657,11 +787,11 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4471</v>
+        <v>4945</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -669,22 +799,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n">
-        <v>352000000</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>78730</v>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>7号屋</t>
+          <t>5号屋</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -703,7 +837,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4470</v>
+        <v>4471</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -716,10 +850,10 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>491693000</v>
+        <v>352000000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>109998</v>
+        <v>78730</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -730,7 +864,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>8号屋</t>
+          <t>6号屋</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -749,7 +883,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5221</v>
+        <v>4391</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -762,10 +896,10 @@
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>730000000</v>
+        <v>506049000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>139820</v>
+        <v>115247</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -776,7 +910,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>9号屋</t>
+          <t>7号屋</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -795,7 +929,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3905</v>
+        <v>4470</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -808,10 +942,10 @@
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>458000000</v>
+        <v>491693000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>117286</v>
+        <v>109998</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -822,7 +956,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>10号屋</t>
+          <t>8号屋</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -837,11 +971,11 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3845</v>
+        <v>5221</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -854,10 +988,10 @@
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>458000000</v>
+        <v>730000000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>119116</v>
+        <v>139820</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -868,7 +1002,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>12号屋</t>
+          <t>9号屋</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -883,11 +1017,11 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4030</v>
+        <v>3905</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -896,14 +1030,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2014-08-14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>412638000</v>
+        <v>458000000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>102392</v>
+        <v>117286</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -914,44 +1048,182 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>10号屋</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>3845</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>458000000</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>119116</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>11号屋</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>3942</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>392074000</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>99461</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>12号屋</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>4030</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>2014-08-14</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>412638000</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>102392</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>15号屋</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>3885</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>已售</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n">
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>450000000</v>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="I14" s="5" t="n">
         <v>115830</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -970,166 +1242,255 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>总价</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2号屋</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>495100000</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>3号屋</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>在售</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>5号屋</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>352000000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>7号屋</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>491693000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>8号屋</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>730000000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>9号屋</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>458000000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>10号屋</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>458000000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>12号屋</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>412638000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>15号屋</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>450000000</v>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Twelve Peaks - 独立屋销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>12 套</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>1 套</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>11 套</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>位置 1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>位置 2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>位置 3</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>位置 4</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>位置 5</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>位置 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>第 1 行</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>1号屋
+4858呎 (4+房)
+(已售)
+$6.67亿
+$137,201/呎</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>2号屋
+4479呎 (4+房)
+(已售)
+$4.95亿
+$110,538/呎</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>3号屋
+4945呎 (4+房)
+(在售)
+招标项目
+-</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>5号屋
+4471呎 (4+房)
+(已售)
+$3.52亿
+$78,730/呎</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>6号屋
+4391呎 (4+房)
+(已售)
+$5.06亿
+$115,247/呎</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>7号屋
+4470呎 (4+房)
+(已售)
+$4.92亿
+$109,998/呎</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>第 2 行</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>8号屋
+5221呎 (4+房)
+(已售)
+$7.30亿
+$139,820/呎</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>9号屋
+3905呎 (4+房)
+(已售)
+$4.58亿
+$117,286/呎</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>10号屋
+3845呎 (3房)
+(已售)
+$4.58亿
+$119,116/呎</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>11号屋
+3942呎 (4+房)
+(已售)
+$3.92亿
+$99,461/呎</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>12号屋
+4030呎 (3房)
+(14年-08月)
+$4.13亿
+$102,392/呎</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>15号屋
+3885呎 (4+房)
+(已售)
+$4.50亿
+$115,830/呎</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/files/港岛-山顶区-Twelve Peaks.xlsx
+++ b/files/港岛-山顶区-Twelve Peaks.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-12-23</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -750,7 +750,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-05</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-02-26</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -938,7 +938,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-02-08</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -984,7 +984,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-12-27</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-12-23</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-02-12</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-11-08</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1374,7 +1374,7 @@
         <is>
           <t>1号屋
 4858呎 (4+房)
-(已售)
+(18年-12月)
 $6.67亿
 $137,201/呎</t>
         </is>
@@ -1383,7 +1383,7 @@
         <is>
           <t>2号屋
 4479呎 (4+房)
-(已售)
+(18年-08月)
 $4.95亿
 $110,538/呎</t>
         </is>
@@ -1401,7 +1401,7 @@
         <is>
           <t>5号屋
 4471呎 (4+房)
-(已售)
+(25年-10月)
 $3.52亿
 $78,730/呎</t>
         </is>
@@ -1410,7 +1410,7 @@
         <is>
           <t>6号屋
 4391呎 (4+房)
-(已售)
+(15年-02月)
 $5.06亿
 $115,247/呎</t>
         </is>
@@ -1419,7 +1419,7 @@
         <is>
           <t>7号屋
 4470呎 (4+房)
-(已售)
+(15年-02月)
 $4.92亿
 $109,998/呎</t>
         </is>
@@ -1435,7 +1435,7 @@
         <is>
           <t>8号屋
 5221呎 (4+房)
-(已售)
+(18年-08月)
 $7.30亿
 $139,820/呎</t>
         </is>
@@ -1444,7 +1444,7 @@
         <is>
           <t>9号屋
 3905呎 (4+房)
-(已售)
+(18年-12月)
 $4.58亿
 $117,286/呎</t>
         </is>
@@ -1453,7 +1453,7 @@
         <is>
           <t>10号屋
 3845呎 (3房)
-(已售)
+(18年-12月)
 $4.58亿
 $119,116/呎</t>
         </is>
@@ -1462,7 +1462,7 @@
         <is>
           <t>11号屋
 3942呎 (4+房)
-(已售)
+(15年-02月)
 $3.92亿
 $99,461/呎</t>
         </is>
@@ -1480,7 +1480,7 @@
         <is>
           <t>15号屋
 3885呎 (4+房)
-(已售)
+(18年-11月)
 $4.50亿
 $115,830/呎</t>
         </is>

--- a/files/港岛-山顶区-Twelve Peaks.xlsx
+++ b/files/港岛-山顶区-Twelve Peaks.xlsx
@@ -184,49 +184,49 @@
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -609,7 +609,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-山顶区-Twelve Peaks.xlsx
+++ b/files/港岛-山顶区-Twelve Peaks.xlsx
@@ -184,49 +184,49 @@
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -609,7 +609,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
